--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1315,7 +1315,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1490,7 +1490,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1561,7 +1561,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -1744,7 +1744,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2106,7 +2106,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="70.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="569">
   <si>
     <t>Property</t>
   </si>
@@ -641,9 +641,9 @@
     <t>このObservationを分類するコード</t>
   </si>
   <si>
-    <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
-第2コード（second）は、歯科を表すコードLP89803-8を設定する。
+    <t>3つのコードを設定する。
+第1コード（first）は、simpleObservationコード体系を必須とし、examを設定する。
+第2コード（second）は、歯科を表すコードLP89803-8を設定する。
 第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
   </si>
   <si>
@@ -833,7 +833,7 @@
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>procedure</t>
+    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1385,8 +1385,8 @@
     <t>特定の歯（歯式）</t>
   </si>
   <si>
-    <t>優先順位は以下の番号を推奨する。
-1.FDI
+    <t>優先順位は以下の番号を推奨する。
+1.FDI
 2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
   </si>
   <si>
@@ -1403,6 +1403,21 @@
   </si>
   <si>
     <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.id</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:bodySiteStatus</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.coding</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.text</t>
   </si>
   <si>
     <t>Observation.method</t>
@@ -2079,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP99"/>
+  <dimension ref="A1:AP104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
@@ -11199,20 +11214,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>448</v>
+        <v>215</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11236,13 +11247,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>451</v>
+        <v>83</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>452</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11260,7 +11271,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>447</v>
+        <v>217</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11272,7 +11283,7 @@
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -11281,10 +11292,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>453</v>
+        <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>454</v>
+        <v>218</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11295,21 +11306,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11321,16 +11332,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>456</v>
+        <v>139</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>457</v>
+        <v>156</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11368,59 +11379,61 @@
         <v>83</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>83</v>
+        <v>223</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>455</v>
+        <v>224</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>460</v>
+        <v>218</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>461</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11429,7 +11442,7 @@
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>83</v>
@@ -11441,17 +11454,15 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>463</v>
+        <v>148</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>464</v>
+        <v>149</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11500,45 +11511,45 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>462</v>
+        <v>224</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>468</v>
+        <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>469</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11558,22 +11569,22 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>471</v>
+        <v>227</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>472</v>
+        <v>230</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>473</v>
+        <v>231</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11622,7 +11633,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>470</v>
+        <v>232</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11634,7 +11645,7 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>474</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11643,10 +11654,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>475</v>
+        <v>233</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>476</v>
+        <v>234</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11657,10 +11668,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11680,19 +11691,23 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>215</v>
+        <v>286</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -11740,7 +11755,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>217</v>
+        <v>290</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11752,7 +11767,7 @@
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -11761,10 +11776,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>218</v>
+        <v>292</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11775,21 +11790,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>83</v>
@@ -11801,18 +11816,20 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>221</v>
+        <v>453</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>222</v>
+        <v>453</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -11836,13 +11853,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>83</v>
+        <v>456</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -11860,19 +11877,19 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>224</v>
+        <v>452</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>83</v>
@@ -11881,10 +11898,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>83</v>
+        <v>458</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>218</v>
+        <v>459</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -11895,46 +11912,44 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>139</v>
+        <v>461</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>481</v>
+        <v>179</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>482</v>
+        <v>179</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -11982,45 +11997,45 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>137</v>
+        <v>465</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>83</v>
+        <v>466</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12043,15 +12058,17 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12100,7 +12117,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12109,7 +12126,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12118,27 +12135,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>83</v>
+        <v>471</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>83</v>
+        <v>474</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12149,7 +12166,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>83</v>
@@ -12161,16 +12178,20 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>492</v>
+        <v>179</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
       </c>
@@ -12218,19 +12239,19 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>106</v>
+        <v>479</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12239,10 +12260,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12253,10 +12274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12279,20 +12300,16 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>496</v>
+        <v>215</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12316,13 +12333,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>500</v>
+        <v>83</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>501</v>
+        <v>83</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12340,7 +12357,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>495</v>
+        <v>217</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12352,19 +12369,19 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>431</v>
+        <v>218</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12375,14 +12392,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12401,20 +12418,18 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>505</v>
+        <v>221</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>506</v>
+        <v>222</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12438,13 +12453,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12462,7 +12477,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>504</v>
+        <v>224</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12474,19 +12489,19 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>431</v>
+        <v>218</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12497,43 +12512,45 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>83</v>
+        <v>485</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>512</v>
+        <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O87" t="s" s="2">
-        <v>515</v>
+        <v>157</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12582,19 +12599,19 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -12606,7 +12623,7 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>516</v>
+        <v>137</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12617,10 +12634,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12643,13 +12660,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>214</v>
+        <v>490</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12700,7 +12717,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12709,7 +12726,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12721,10 +12738,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12735,10 +12752,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12749,7 +12766,7 @@
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -12758,20 +12775,18 @@
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -12820,16 +12835,16 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -12841,10 +12856,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>525</v>
+        <v>494</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12855,10 +12870,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12869,7 +12884,7 @@
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
@@ -12878,21 +12893,23 @@
         <v>83</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>528</v>
+        <v>198</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>179</v>
+        <v>501</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>179</v>
+        <v>502</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
       </c>
@@ -12916,13 +12933,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>83</v>
+        <v>505</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>83</v>
+        <v>506</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -12940,13 +12957,13 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
@@ -12958,13 +12975,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>83</v>
+        <v>507</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>530</v>
+        <v>431</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12975,10 +12992,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12998,22 +13015,22 @@
         <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>471</v>
+        <v>198</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>179</v>
+        <v>510</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>179</v>
+        <v>511</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13038,13 +13055,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>83</v>
+        <v>514</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>83</v>
+        <v>515</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13062,7 +13079,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13080,13 +13097,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>83</v>
+        <v>507</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>535</v>
+        <v>431</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13097,10 +13114,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13123,16 +13140,18 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>214</v>
+        <v>517</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>215</v>
+        <v>518</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>216</v>
+        <v>519</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13180,7 +13199,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>217</v>
+        <v>516</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13192,7 +13211,7 @@
         <v>83</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>83</v>
@@ -13204,7 +13223,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>218</v>
+        <v>521</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13215,21 +13234,21 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>83</v>
@@ -13241,17 +13260,15 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>221</v>
+        <v>523</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13300,19 +13317,19 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>224</v>
+        <v>522</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>83</v>
@@ -13321,10 +13338,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>218</v>
+        <v>525</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13335,14 +13352,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13355,26 +13372,24 @@
         <v>83</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>139</v>
+        <v>527</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13422,7 +13437,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13434,7 +13449,7 @@
         <v>83</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>83</v>
@@ -13443,10 +13458,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>137</v>
+        <v>531</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13457,10 +13472,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13468,10 +13483,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>83</v>
@@ -13483,20 +13498,18 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>198</v>
+        <v>533</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>540</v>
+        <v>179</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>541</v>
+        <v>179</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>83</v>
       </c>
@@ -13520,13 +13533,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13544,13 +13557,13 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>83</v>
@@ -13562,16 +13575,16 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>543</v>
+        <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>337</v>
+        <v>530</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>338</v>
+        <v>535</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>339</v>
+        <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -13579,10 +13592,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13593,7 +13606,7 @@
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
@@ -13605,19 +13618,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>545</v>
+        <v>476</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>546</v>
+        <v>179</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>547</v>
+        <v>179</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>407</v>
+        <v>538</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13666,13 +13679,13 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>83</v>
@@ -13684,27 +13697,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>549</v>
+        <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>411</v>
+        <v>539</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>412</v>
+        <v>540</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>413</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13727,20 +13740,16 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>551</v>
+        <v>215</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>83</v>
       </c>
@@ -13764,13 +13773,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>420</v>
+        <v>83</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13788,7 +13797,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>550</v>
+        <v>217</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13797,10 +13806,10 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>421</v>
+        <v>83</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>83</v>
@@ -13809,10 +13818,10 @@
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>422</v>
+        <v>218</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13823,14 +13832,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>424</v>
+        <v>153</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13849,20 +13858,18 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>555</v>
+        <v>221</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>556</v>
+        <v>222</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -13886,13 +13893,13 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>427</v>
+        <v>83</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>428</v>
+        <v>83</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -13910,7 +13917,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>554</v>
+        <v>224</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13922,37 +13929,37 @@
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>429</v>
+        <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>431</v>
+        <v>218</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>432</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>83</v>
+        <v>485</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13965,25 +13972,25 @@
         <v>83</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>560</v>
+        <v>486</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>561</v>
+        <v>487</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>562</v>
+        <v>156</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>563</v>
+        <v>157</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14032,7 +14039,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>559</v>
+        <v>488</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14044,24 +14051,634 @@
         <v>83</v>
       </c>
       <c r="AJ99" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP99" t="s" s="2">
+      <c r="AK100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP104" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -642,7 +642,7 @@
   </si>
   <si>
     <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、examを設定する。
+第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
 第2コード（second）は、歯科を表すコードLP89803-8を設定する。
 第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
   </si>
@@ -833,7 +833,7 @@
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>exam</t>
+    <t>procedure</t>
   </si>
   <si>
     <t>Coding.code</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -642,7 +642,7 @@
   </si>
   <si>
     <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
+第1コード（first）は、simpleObservationコード体系を必須とし、examを設定する。
 第2コード（second）は、歯科を表すコードLP89803-8を設定する。
 第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
   </si>
@@ -833,7 +833,7 @@
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>procedure</t>
+    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2024-06-24</t>
   </si>
   <si>
     <t>Publisher</t>
